--- a/MetaData/Giro d'Italia.xlsx
+++ b/MetaData/Giro d'Italia.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="2009" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="731">
   <si>
     <t>NUM</t>
   </si>
@@ -704,9 +704,6 @@
   </si>
   <si>
     <t>3511.12 Km</t>
-  </si>
-  <si>
-    <t>P</t>
   </si>
   <si>
     <t>Saturday 5 May 2012</t>
@@ -3383,13 +3380,13 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2" t="s">
         <v>605</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>606</v>
-      </c>
-      <c r="E2" t="s">
-        <v>607</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3412,13 +3409,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D3" t="s">
         <v>608</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>609</v>
-      </c>
-      <c r="E3" t="s">
-        <v>610</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3441,13 +3438,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D4" t="s">
         <v>611</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>612</v>
-      </c>
-      <c r="E4" t="s">
-        <v>613</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3470,13 +3467,13 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>613</v>
+      </c>
+      <c r="D5" t="s">
         <v>614</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>615</v>
-      </c>
-      <c r="E5" t="s">
-        <v>616</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -3499,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
+        <v>616</v>
+      </c>
+      <c r="D6" t="s">
         <v>617</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>618</v>
-      </c>
-      <c r="E6" t="s">
-        <v>619</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -3528,13 +3525,13 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D7" t="s">
         <v>620</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>621</v>
-      </c>
-      <c r="E7" t="s">
-        <v>622</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -3557,13 +3554,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>622</v>
+      </c>
+      <c r="D8" t="s">
         <v>623</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>624</v>
-      </c>
-      <c r="E8" t="s">
-        <v>625</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -3586,13 +3583,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
+        <v>625</v>
+      </c>
+      <c r="D9" t="s">
         <v>626</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>627</v>
-      </c>
-      <c r="E9" t="s">
-        <v>628</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -3615,13 +3612,13 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
+        <v>628</v>
+      </c>
+      <c r="D10" t="s">
         <v>629</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>630</v>
-      </c>
-      <c r="E10" t="s">
-        <v>631</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -3644,13 +3641,13 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
+        <v>631</v>
+      </c>
+      <c r="D11" t="s">
         <v>632</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>633</v>
-      </c>
-      <c r="E11" t="s">
-        <v>634</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -3673,13 +3670,13 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
+        <v>634</v>
+      </c>
+      <c r="D12" t="s">
         <v>635</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>636</v>
-      </c>
-      <c r="E12" t="s">
-        <v>637</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -3702,13 +3699,13 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
+        <v>637</v>
+      </c>
+      <c r="D13" t="s">
         <v>638</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>639</v>
-      </c>
-      <c r="E13" t="s">
-        <v>640</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -3731,13 +3728,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
+        <v>640</v>
+      </c>
+      <c r="D14" t="s">
         <v>641</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>642</v>
-      </c>
-      <c r="E14" t="s">
-        <v>643</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -3760,13 +3757,13 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>643</v>
+      </c>
+      <c r="D15" t="s">
         <v>644</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>645</v>
-      </c>
-      <c r="E15" t="s">
-        <v>646</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3789,13 +3786,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
+        <v>646</v>
+      </c>
+      <c r="D16" t="s">
         <v>647</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>648</v>
-      </c>
-      <c r="E16" t="s">
-        <v>649</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -3818,13 +3815,13 @@
         <v>47</v>
       </c>
       <c r="C17" t="s">
+        <v>649</v>
+      </c>
+      <c r="D17" t="s">
         <v>650</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>651</v>
-      </c>
-      <c r="E17" t="s">
-        <v>652</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -3847,13 +3844,13 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>652</v>
+      </c>
+      <c r="D18" t="s">
         <v>653</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>654</v>
-      </c>
-      <c r="E18" t="s">
-        <v>655</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3876,13 +3873,13 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
+        <v>655</v>
+      </c>
+      <c r="D19" t="s">
         <v>656</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>657</v>
-      </c>
-      <c r="E19" t="s">
-        <v>658</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3905,13 +3902,13 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>658</v>
+      </c>
+      <c r="D20" t="s">
         <v>659</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>660</v>
-      </c>
-      <c r="E20" t="s">
-        <v>661</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3934,13 +3931,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>661</v>
+      </c>
+      <c r="D21" t="s">
         <v>662</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>663</v>
-      </c>
-      <c r="E21" t="s">
-        <v>664</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -3963,13 +3960,13 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
+        <v>664</v>
+      </c>
+      <c r="D22" t="s">
         <v>665</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>666</v>
-      </c>
-      <c r="E22" t="s">
-        <v>667</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -3989,7 +3986,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -4176,13 +4173,13 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D2" t="s">
         <v>669</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>670</v>
-      </c>
-      <c r="E2" t="s">
-        <v>671</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4205,13 +4202,13 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D3" t="s">
         <v>672</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>673</v>
-      </c>
-      <c r="E3" t="s">
-        <v>674</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4234,13 +4231,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>674</v>
+      </c>
+      <c r="D4" t="s">
         <v>675</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>676</v>
-      </c>
-      <c r="E4" t="s">
-        <v>677</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4263,13 +4260,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
+        <v>677</v>
+      </c>
+      <c r="D5" t="s">
         <v>678</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>679</v>
-      </c>
-      <c r="E5" t="s">
-        <v>680</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -4292,13 +4289,13 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>680</v>
+      </c>
+      <c r="D6" t="s">
         <v>681</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>682</v>
-      </c>
-      <c r="E6" t="s">
-        <v>683</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4321,13 +4318,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
+        <v>683</v>
+      </c>
+      <c r="D7" t="s">
         <v>684</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>685</v>
-      </c>
-      <c r="E7" t="s">
-        <v>686</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -4350,13 +4347,13 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
+        <v>686</v>
+      </c>
+      <c r="D8" t="s">
         <v>687</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>688</v>
-      </c>
-      <c r="E8" t="s">
-        <v>689</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -4379,13 +4376,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
+        <v>689</v>
+      </c>
+      <c r="D9" t="s">
         <v>690</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>691</v>
-      </c>
-      <c r="E9" t="s">
-        <v>692</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -4408,13 +4405,13 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
+        <v>692</v>
+      </c>
+      <c r="D10" t="s">
         <v>693</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>694</v>
-      </c>
-      <c r="E10" t="s">
-        <v>695</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -4437,13 +4434,13 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>695</v>
+      </c>
+      <c r="D11" t="s">
         <v>696</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>697</v>
-      </c>
-      <c r="E11" t="s">
-        <v>698</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -4466,13 +4463,13 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
+        <v>698</v>
+      </c>
+      <c r="D12" t="s">
         <v>699</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>700</v>
-      </c>
-      <c r="E12" t="s">
-        <v>701</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -4495,13 +4492,13 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -4524,13 +4521,13 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
+        <v>703</v>
+      </c>
+      <c r="D14" t="s">
         <v>704</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>705</v>
-      </c>
-      <c r="E14" t="s">
-        <v>706</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -4553,13 +4550,13 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>706</v>
+      </c>
+      <c r="D15" t="s">
         <v>707</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>708</v>
-      </c>
-      <c r="E15" t="s">
-        <v>709</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -4582,13 +4579,13 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
+        <v>709</v>
+      </c>
+      <c r="D16" t="s">
         <v>710</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>711</v>
-      </c>
-      <c r="E16" t="s">
-        <v>712</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -4611,13 +4608,13 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>712</v>
+      </c>
+      <c r="D17" t="s">
         <v>713</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>714</v>
-      </c>
-      <c r="E17" t="s">
-        <v>715</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -4640,13 +4637,13 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
+        <v>715</v>
+      </c>
+      <c r="D18" t="s">
         <v>716</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>717</v>
-      </c>
-      <c r="E18" t="s">
-        <v>718</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -4669,13 +4666,13 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
+        <v>718</v>
+      </c>
+      <c r="D19" t="s">
         <v>719</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>720</v>
-      </c>
-      <c r="E19" t="s">
-        <v>721</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -4698,13 +4695,13 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>721</v>
+      </c>
+      <c r="D20" t="s">
         <v>722</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>723</v>
-      </c>
-      <c r="E20" t="s">
-        <v>724</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -4727,13 +4724,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>724</v>
+      </c>
+      <c r="D21" t="s">
         <v>725</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>726</v>
-      </c>
-      <c r="E21" t="s">
-        <v>727</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -4756,13 +4753,13 @@
         <v>47</v>
       </c>
       <c r="C22" t="s">
+        <v>727</v>
+      </c>
+      <c r="D22" t="s">
         <v>728</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>729</v>
-      </c>
-      <c r="E22" t="s">
-        <v>730</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -4782,7 +4779,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -6548,20 +6545,20 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>225</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" t="s">
         <v>226</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>227</v>
-      </c>
-      <c r="E2" t="s">
-        <v>228</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -6578,19 +6575,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" t="s">
         <v>229</v>
-      </c>
-      <c r="D3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E3" t="s">
-        <v>230</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -6607,19 +6604,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" t="s">
         <v>231</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>232</v>
-      </c>
-      <c r="E4" t="s">
-        <v>233</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6636,19 +6633,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D5" t="s">
         <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -6665,19 +6662,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" t="s">
         <v>236</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>237</v>
-      </c>
-      <c r="E6" t="s">
-        <v>238</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6694,19 +6691,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" t="s">
         <v>239</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>240</v>
-      </c>
-      <c r="E7" t="s">
-        <v>241</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -6723,19 +6720,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" t="s">
         <v>242</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>243</v>
-      </c>
-      <c r="E8" t="s">
-        <v>244</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -6752,19 +6749,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" t="s">
         <v>245</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>246</v>
-      </c>
-      <c r="E9" t="s">
-        <v>247</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -6781,19 +6778,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" t="s">
         <v>248</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>249</v>
-      </c>
-      <c r="E10" t="s">
-        <v>250</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -6810,19 +6807,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" t="s">
         <v>251</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>252</v>
-      </c>
-      <c r="E11" t="s">
-        <v>253</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -6839,19 +6836,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
+        <v>253</v>
+      </c>
+      <c r="D12" t="s">
         <v>254</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>255</v>
-      </c>
-      <c r="E12" t="s">
-        <v>256</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -6868,19 +6865,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" t="s">
         <v>257</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>258</v>
-      </c>
-      <c r="E13" t="s">
-        <v>259</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -6897,19 +6894,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" t="s">
         <v>260</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>261</v>
-      </c>
-      <c r="E14" t="s">
-        <v>262</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -6926,19 +6923,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" t="s">
         <v>263</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>264</v>
-      </c>
-      <c r="E15" t="s">
-        <v>265</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -6955,19 +6952,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" t="s">
         <v>266</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>267</v>
-      </c>
-      <c r="E16" t="s">
-        <v>268</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -6984,19 +6981,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" t="s">
         <v>269</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>270</v>
-      </c>
-      <c r="E17" t="s">
-        <v>271</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -7013,19 +7010,19 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
+        <v>271</v>
+      </c>
+      <c r="D18" t="s">
         <v>272</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>273</v>
-      </c>
-      <c r="E18" t="s">
-        <v>274</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -7042,19 +7039,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" t="s">
         <v>275</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>276</v>
-      </c>
-      <c r="E19" t="s">
-        <v>277</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -7071,19 +7068,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" t="s">
         <v>278</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>279</v>
-      </c>
-      <c r="E20" t="s">
-        <v>280</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -7100,19 +7097,19 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D21" t="s">
         <v>281</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>282</v>
-      </c>
-      <c r="E21" t="s">
-        <v>283</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -7129,19 +7126,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>47</v>
       </c>
       <c r="C22" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" t="s">
         <v>284</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>285</v>
-      </c>
-      <c r="E22" t="s">
-        <v>286</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -7161,7 +7158,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -7348,13 +7345,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" t="s">
         <v>288</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>289</v>
-      </c>
-      <c r="E2" t="s">
-        <v>290</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -7377,13 +7374,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" t="s">
         <v>291</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>292</v>
-      </c>
-      <c r="E3" t="s">
-        <v>293</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -7406,13 +7403,13 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" t="s">
         <v>294</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>295</v>
-      </c>
-      <c r="E4" t="s">
-        <v>296</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -7435,13 +7432,13 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D5" t="s">
         <v>297</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>298</v>
-      </c>
-      <c r="E5" t="s">
-        <v>299</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -7464,13 +7461,13 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D6" t="s">
         <v>300</v>
       </c>
-      <c r="D6" t="s">
-        <v>301</v>
-      </c>
       <c r="E6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -7493,13 +7490,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" t="s">
         <v>302</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>303</v>
-      </c>
-      <c r="E7" t="s">
-        <v>304</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -7522,13 +7519,13 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" t="s">
         <v>305</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>306</v>
-      </c>
-      <c r="E8" t="s">
-        <v>307</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -7551,13 +7548,13 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" t="s">
         <v>308</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>309</v>
-      </c>
-      <c r="E9" t="s">
-        <v>310</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -7580,13 +7577,13 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" t="s">
         <v>311</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>312</v>
-      </c>
-      <c r="E10" t="s">
-        <v>313</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -7609,13 +7606,13 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" t="s">
         <v>314</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>315</v>
-      </c>
-      <c r="E11" t="s">
-        <v>316</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -7638,13 +7635,13 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
+        <v>316</v>
+      </c>
+      <c r="D12" t="s">
         <v>317</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>318</v>
-      </c>
-      <c r="E12" t="s">
-        <v>319</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -7667,13 +7664,13 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
+        <v>319</v>
+      </c>
+      <c r="D13" t="s">
         <v>320</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>321</v>
-      </c>
-      <c r="E13" t="s">
-        <v>322</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -7696,13 +7693,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D14" t="s">
         <v>323</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>324</v>
-      </c>
-      <c r="E14" t="s">
-        <v>325</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -7725,13 +7722,13 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" t="s">
         <v>326</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>327</v>
-      </c>
-      <c r="E15" t="s">
-        <v>328</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -7754,13 +7751,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D16" t="s">
         <v>329</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>330</v>
-      </c>
-      <c r="E16" t="s">
-        <v>331</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -7783,13 +7780,13 @@
         <v>29</v>
       </c>
       <c r="C17" t="s">
+        <v>331</v>
+      </c>
+      <c r="D17" t="s">
         <v>332</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>333</v>
-      </c>
-      <c r="E17" t="s">
-        <v>334</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -7812,13 +7809,13 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>334</v>
+      </c>
+      <c r="D18" t="s">
         <v>335</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>336</v>
-      </c>
-      <c r="E18" t="s">
-        <v>337</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -7841,13 +7838,13 @@
         <v>47</v>
       </c>
       <c r="C19" t="s">
+        <v>337</v>
+      </c>
+      <c r="D19" t="s">
         <v>338</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>339</v>
-      </c>
-      <c r="E19" t="s">
-        <v>340</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -7870,13 +7867,13 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D20" t="s">
         <v>341</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>342</v>
-      </c>
-      <c r="E20" t="s">
-        <v>343</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -7899,13 +7896,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>343</v>
+      </c>
+      <c r="D21" t="s">
         <v>344</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>345</v>
-      </c>
-      <c r="E21" t="s">
-        <v>346</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -7928,13 +7925,13 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" t="s">
         <v>347</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>348</v>
-      </c>
-      <c r="E22" t="s">
-        <v>349</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -7954,7 +7951,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -8141,13 +8138,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D2" t="s">
         <v>351</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>352</v>
-      </c>
-      <c r="E2" t="s">
-        <v>353</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8170,13 +8167,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" t="s">
         <v>354</v>
-      </c>
-      <c r="D3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E3" t="s">
-        <v>355</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -8199,13 +8196,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" t="s">
         <v>356</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>357</v>
-      </c>
-      <c r="E4" t="s">
-        <v>358</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -8228,13 +8225,13 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D5" t="s">
         <v>359</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>360</v>
-      </c>
-      <c r="E5" t="s">
-        <v>361</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -8257,13 +8254,13 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" t="s">
         <v>362</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>363</v>
-      </c>
-      <c r="E6" t="s">
-        <v>364</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -8286,13 +8283,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" t="s">
         <v>365</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>366</v>
-      </c>
-      <c r="E7" t="s">
-        <v>367</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -8315,13 +8312,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>367</v>
+      </c>
+      <c r="D8" t="s">
         <v>368</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>369</v>
-      </c>
-      <c r="E8" t="s">
-        <v>370</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -8344,13 +8341,13 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>370</v>
+      </c>
+      <c r="D9" t="s">
         <v>371</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>372</v>
-      </c>
-      <c r="E9" t="s">
-        <v>373</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -8373,13 +8370,13 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>373</v>
+      </c>
+      <c r="D10" t="s">
         <v>374</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>375</v>
-      </c>
-      <c r="E10" t="s">
-        <v>376</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -8402,13 +8399,13 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>376</v>
+      </c>
+      <c r="D11" t="s">
         <v>377</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>378</v>
-      </c>
-      <c r="E11" t="s">
-        <v>379</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -8431,13 +8428,13 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" t="s">
         <v>380</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>381</v>
-      </c>
-      <c r="E12" t="s">
-        <v>382</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -8460,13 +8457,13 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
+        <v>382</v>
+      </c>
+      <c r="D13" t="s">
         <v>383</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>384</v>
-      </c>
-      <c r="E13" t="s">
-        <v>385</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -8489,13 +8486,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
+        <v>385</v>
+      </c>
+      <c r="D14" t="s">
         <v>386</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>387</v>
-      </c>
-      <c r="E14" t="s">
-        <v>388</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -8518,13 +8515,13 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>388</v>
+      </c>
+      <c r="D15" t="s">
         <v>389</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>390</v>
-      </c>
-      <c r="E15" t="s">
-        <v>391</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -8547,13 +8544,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
+        <v>391</v>
+      </c>
+      <c r="D16" t="s">
         <v>392</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>393</v>
-      </c>
-      <c r="E16" t="s">
-        <v>394</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -8576,13 +8573,13 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>394</v>
+      </c>
+      <c r="D17" t="s">
         <v>395</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>396</v>
-      </c>
-      <c r="E17" t="s">
-        <v>397</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -8605,13 +8602,13 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" t="s">
         <v>398</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>399</v>
-      </c>
-      <c r="E18" t="s">
-        <v>400</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -8634,13 +8631,13 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
+        <v>400</v>
+      </c>
+      <c r="D19" t="s">
         <v>401</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>402</v>
-      </c>
-      <c r="E19" t="s">
-        <v>403</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -8663,13 +8660,13 @@
         <v>47</v>
       </c>
       <c r="C20" t="s">
+        <v>403</v>
+      </c>
+      <c r="D20" t="s">
         <v>404</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>405</v>
-      </c>
-      <c r="E20" t="s">
-        <v>406</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -8692,13 +8689,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D21" t="s">
         <v>407</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>408</v>
-      </c>
-      <c r="E21" t="s">
-        <v>409</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -8721,13 +8718,13 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
+        <v>409</v>
+      </c>
+      <c r="D22" t="s">
         <v>410</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>411</v>
-      </c>
-      <c r="E22" t="s">
-        <v>412</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -8747,7 +8744,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -8934,13 +8931,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D2" t="s">
         <v>414</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>415</v>
-      </c>
-      <c r="E2" t="s">
-        <v>416</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8963,13 +8960,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D3" t="s">
         <v>417</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>418</v>
-      </c>
-      <c r="E3" t="s">
-        <v>419</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -8992,13 +8989,13 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" t="s">
         <v>420</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>421</v>
-      </c>
-      <c r="E4" t="s">
-        <v>422</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -9021,13 +9018,13 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D5" t="s">
         <v>423</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>424</v>
-      </c>
-      <c r="E5" t="s">
-        <v>425</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -9050,13 +9047,13 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D6" t="s">
         <v>426</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>427</v>
-      </c>
-      <c r="E6" t="s">
-        <v>428</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -9079,13 +9076,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D7" t="s">
         <v>429</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>430</v>
-      </c>
-      <c r="E7" t="s">
-        <v>431</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -9108,13 +9105,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D8" t="s">
         <v>432</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>433</v>
-      </c>
-      <c r="E8" t="s">
-        <v>434</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -9137,13 +9134,13 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9" t="s">
         <v>435</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>436</v>
-      </c>
-      <c r="E9" t="s">
-        <v>437</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -9166,13 +9163,13 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D10" t="s">
         <v>438</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>439</v>
-      </c>
-      <c r="E10" t="s">
-        <v>440</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -9195,13 +9192,13 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" t="s">
         <v>441</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>442</v>
-      </c>
-      <c r="E11" t="s">
-        <v>443</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -9224,13 +9221,13 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
+        <v>443</v>
+      </c>
+      <c r="D12" t="s">
         <v>444</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>445</v>
-      </c>
-      <c r="E12" t="s">
-        <v>446</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -9253,13 +9250,13 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
+        <v>446</v>
+      </c>
+      <c r="D13" t="s">
         <v>447</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>448</v>
-      </c>
-      <c r="E13" t="s">
-        <v>449</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -9282,13 +9279,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
+        <v>449</v>
+      </c>
+      <c r="D14" t="s">
         <v>450</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>451</v>
-      </c>
-      <c r="E14" t="s">
-        <v>452</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -9311,13 +9308,13 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
+        <v>452</v>
+      </c>
+      <c r="D15" t="s">
         <v>453</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>454</v>
-      </c>
-      <c r="E15" t="s">
-        <v>455</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -9340,13 +9337,13 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D16" t="s">
         <v>456</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>457</v>
-      </c>
-      <c r="E16" t="s">
-        <v>458</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -9369,13 +9366,13 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>458</v>
+      </c>
+      <c r="D17" t="s">
         <v>459</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>460</v>
-      </c>
-      <c r="E17" t="s">
-        <v>461</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -9398,13 +9395,13 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>461</v>
+      </c>
+      <c r="D18" t="s">
         <v>462</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>463</v>
-      </c>
-      <c r="E18" t="s">
-        <v>464</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -9427,13 +9424,13 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
+        <v>464</v>
+      </c>
+      <c r="D19" t="s">
         <v>465</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>466</v>
-      </c>
-      <c r="E19" t="s">
-        <v>467</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -9456,13 +9453,13 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>467</v>
+      </c>
+      <c r="D20" t="s">
         <v>468</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>469</v>
-      </c>
-      <c r="E20" t="s">
-        <v>470</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -9485,13 +9482,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D21" t="s">
         <v>471</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>472</v>
-      </c>
-      <c r="E21" t="s">
-        <v>473</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -9514,13 +9511,13 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
+        <v>473</v>
+      </c>
+      <c r="D22" t="s">
         <v>474</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>475</v>
-      </c>
-      <c r="E22" t="s">
-        <v>476</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -9540,7 +9537,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -9720,20 +9717,20 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>225</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
       <c r="C2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D2" t="s">
         <v>478</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>479</v>
-      </c>
-      <c r="E2" t="s">
-        <v>480</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -9750,19 +9747,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D3" t="s">
         <v>481</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>482</v>
-      </c>
-      <c r="E3" t="s">
-        <v>483</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -9779,19 +9776,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>483</v>
+      </c>
+      <c r="D4" t="s">
         <v>484</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>485</v>
-      </c>
-      <c r="E4" t="s">
-        <v>486</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -9808,19 +9805,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
       <c r="C5" t="s">
+        <v>486</v>
+      </c>
+      <c r="D5" t="s">
         <v>487</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>488</v>
-      </c>
-      <c r="E5" t="s">
-        <v>489</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -9837,19 +9834,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D6" t="s">
         <v>490</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>491</v>
-      </c>
-      <c r="E6" t="s">
-        <v>492</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -9866,19 +9863,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
+        <v>492</v>
+      </c>
+      <c r="D7" t="s">
         <v>493</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>494</v>
-      </c>
-      <c r="E7" t="s">
-        <v>495</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -9895,19 +9892,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D8" t="s">
         <v>496</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>497</v>
-      </c>
-      <c r="E8" t="s">
-        <v>498</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -9924,19 +9921,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D9" t="s">
         <v>499</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>500</v>
-      </c>
-      <c r="E9" t="s">
-        <v>501</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -9953,19 +9950,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
       </c>
       <c r="C10" t="s">
+        <v>501</v>
+      </c>
+      <c r="D10" t="s">
         <v>502</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>503</v>
-      </c>
-      <c r="E10" t="s">
-        <v>504</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -9982,19 +9979,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D11" t="s">
         <v>505</v>
       </c>
-      <c r="D11" t="s">
-        <v>506</v>
-      </c>
       <c r="E11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -10011,19 +10008,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D12" t="s">
         <v>507</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>508</v>
-      </c>
-      <c r="E12" t="s">
-        <v>509</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -10040,19 +10037,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
+        <v>509</v>
+      </c>
+      <c r="D13" t="s">
         <v>510</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>511</v>
-      </c>
-      <c r="E13" t="s">
-        <v>512</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -10069,19 +10066,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
+        <v>512</v>
+      </c>
+      <c r="D14" t="s">
         <v>513</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>514</v>
-      </c>
-      <c r="E14" t="s">
-        <v>515</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -10098,19 +10095,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>515</v>
+      </c>
+      <c r="D15" t="s">
         <v>516</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>517</v>
-      </c>
-      <c r="E15" t="s">
-        <v>518</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -10127,19 +10124,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
       </c>
       <c r="C16" t="s">
+        <v>518</v>
+      </c>
+      <c r="D16" t="s">
         <v>519</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>520</v>
-      </c>
-      <c r="E16" t="s">
-        <v>521</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -10156,19 +10153,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>521</v>
+      </c>
+      <c r="D17" t="s">
         <v>522</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>523</v>
-      </c>
-      <c r="E17" t="s">
-        <v>524</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -10185,19 +10182,19 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
+        <v>524</v>
+      </c>
+      <c r="D18" t="s">
         <v>525</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>526</v>
-      </c>
-      <c r="E18" t="s">
-        <v>527</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -10214,19 +10211,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
+        <v>527</v>
+      </c>
+      <c r="D19" t="s">
         <v>528</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>529</v>
-      </c>
-      <c r="E19" t="s">
-        <v>530</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -10243,19 +10240,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>530</v>
+      </c>
+      <c r="D20" t="s">
         <v>531</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>532</v>
-      </c>
-      <c r="E20" t="s">
-        <v>533</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -10272,19 +10269,19 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>533</v>
+      </c>
+      <c r="D21" t="s">
         <v>534</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>535</v>
-      </c>
-      <c r="E21" t="s">
-        <v>536</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -10301,19 +10298,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
+        <v>536</v>
+      </c>
+      <c r="D22" t="s">
         <v>537</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>538</v>
-      </c>
-      <c r="E22" t="s">
-        <v>539</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -10333,7 +10330,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -10520,13 +10517,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D2" t="s">
         <v>541</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>542</v>
-      </c>
-      <c r="E2" t="s">
-        <v>543</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -10549,13 +10546,13 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D3" t="s">
         <v>544</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>545</v>
-      </c>
-      <c r="E3" t="s">
-        <v>546</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -10578,13 +10575,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D4" t="s">
         <v>547</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>548</v>
-      </c>
-      <c r="E4" t="s">
-        <v>549</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -10607,13 +10604,13 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>549</v>
+      </c>
+      <c r="D5" t="s">
         <v>550</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>551</v>
-      </c>
-      <c r="E5" t="s">
-        <v>552</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -10636,13 +10633,13 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>552</v>
+      </c>
+      <c r="D6" t="s">
         <v>553</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>554</v>
-      </c>
-      <c r="E6" t="s">
-        <v>555</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -10665,13 +10662,13 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D7" t="s">
         <v>556</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>557</v>
-      </c>
-      <c r="E7" t="s">
-        <v>558</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -10694,13 +10691,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D8" t="s">
         <v>559</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>560</v>
-      </c>
-      <c r="E8" t="s">
-        <v>561</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -10723,13 +10720,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
+        <v>561</v>
+      </c>
+      <c r="D9" t="s">
         <v>562</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>563</v>
-      </c>
-      <c r="E9" t="s">
-        <v>564</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -10752,13 +10749,13 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D10" t="s">
         <v>565</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>566</v>
-      </c>
-      <c r="E10" t="s">
-        <v>567</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -10781,13 +10778,13 @@
         <v>47</v>
       </c>
       <c r="C11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D11" t="s">
         <v>568</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>569</v>
-      </c>
-      <c r="E11" t="s">
-        <v>570</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -10810,13 +10807,13 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
+        <v>570</v>
+      </c>
+      <c r="D12" t="s">
         <v>571</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>572</v>
-      </c>
-      <c r="E12" t="s">
-        <v>573</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -10839,13 +10836,13 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
+        <v>573</v>
+      </c>
+      <c r="D13" t="s">
         <v>574</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>575</v>
-      </c>
-      <c r="E13" t="s">
-        <v>576</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -10868,13 +10865,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
+        <v>576</v>
+      </c>
+      <c r="D14" t="s">
         <v>577</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>578</v>
-      </c>
-      <c r="E14" t="s">
-        <v>579</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -10897,13 +10894,13 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>579</v>
+      </c>
+      <c r="D15" t="s">
         <v>580</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>581</v>
-      </c>
-      <c r="E15" t="s">
-        <v>582</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -10926,13 +10923,13 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
+        <v>582</v>
+      </c>
+      <c r="D16" t="s">
         <v>583</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>584</v>
-      </c>
-      <c r="E16" t="s">
-        <v>585</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -10955,13 +10952,13 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>585</v>
+      </c>
+      <c r="D17" t="s">
         <v>586</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>587</v>
-      </c>
-      <c r="E17" t="s">
-        <v>588</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -10984,13 +10981,13 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
+        <v>588</v>
+      </c>
+      <c r="D18" t="s">
         <v>589</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>590</v>
-      </c>
-      <c r="E18" t="s">
-        <v>591</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -11013,13 +11010,13 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
+        <v>591</v>
+      </c>
+      <c r="D19" t="s">
         <v>592</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>593</v>
-      </c>
-      <c r="E19" t="s">
-        <v>594</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -11042,13 +11039,13 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>594</v>
+      </c>
+      <c r="D20" t="s">
         <v>595</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>596</v>
-      </c>
-      <c r="E20" t="s">
-        <v>597</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -11071,13 +11068,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>597</v>
+      </c>
+      <c r="D21" t="s">
         <v>598</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>599</v>
-      </c>
-      <c r="E21" t="s">
-        <v>600</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -11100,13 +11097,13 @@
         <v>47</v>
       </c>
       <c r="C22" t="s">
+        <v>600</v>
+      </c>
+      <c r="D22" t="s">
         <v>601</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>602</v>
-      </c>
-      <c r="E22" t="s">
-        <v>603</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -11126,7 +11123,7 @@
         <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
